--- a/Resources/Sheet/TinhHinhDonVi.xlsx
+++ b/Resources/Sheet/TinhHinhDonVi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7508C2DC-ED05-4000-81CD-E05935CA38C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5D8C40-7295-4B1C-B903-1A5D186BF23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TinhHinhVc" sheetId="15" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="87">
   <si>
     <t>Lựu đạn</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>Súng bộ binh</t>
+  </si>
+  <si>
+    <t>1. Quy định dự trữ, tiêu thụ, bổ sung vật chất</t>
   </si>
 </sst>
 </file>
@@ -341,7 +344,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -364,63 +367,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -459,16 +410,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1334,108 +1279,97 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB73341-358E-4E08-B0AC-7C6EA0655E0C}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="43.28515625" customWidth="1"/>
+    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" spans="1:8" ht="18.75">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D2" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G2" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" spans="1:8" ht="37.5">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="17"/>
+    </row>
+    <row r="3" spans="1:8" ht="37.5">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75">
-      <c r="A3" s="6" t="s">
+    <row r="4" spans="1:8" ht="18.75">
+      <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" ht="18.75">
-      <c r="A4" s="8">
-        <v>1</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="8">
-        <f>F4+G4+H4</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1.45</v>
-      </c>
-      <c r="F4" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:8" ht="18.75">
       <c r="A5" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>62</v>
       </c>
       <c r="D5" s="8">
         <f>F5+G5+H5</f>
-        <v>1.7</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="E5" s="4">
         <v>1.45</v>
       </c>
       <c r="F5" s="4">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4">
@@ -1444,16 +1378,16 @@
     </row>
     <row r="6" spans="1:8" ht="18.75">
       <c r="A6" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>62</v>
       </c>
       <c r="D6" s="8">
-        <f>F6+G6+H6</f>
+        <f t="shared" ref="D6:D29" si="0">F6+G6+H6</f>
         <v>1.7</v>
       </c>
       <c r="E6" s="4">
@@ -1469,73 +1403,73 @@
     </row>
     <row r="7" spans="1:8" ht="18.75">
       <c r="A7" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>62</v>
       </c>
       <c r="D7" s="8">
-        <f>F7+G7+H7</f>
-        <v>2.2999999999999998</v>
+        <f t="shared" si="0"/>
+        <v>1.7</v>
       </c>
       <c r="E7" s="4">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="F7" s="4">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4">
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="18.75">
       <c r="A8" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C8" s="8" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="8">
-        <f>F8+G8+H8</f>
-        <v>1.35</v>
+        <f t="shared" si="0"/>
+        <v>2.2999999999999998</v>
       </c>
       <c r="E8" s="4">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="F8" s="4">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18.75">
       <c r="A9" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="8">
-        <f>F9+G9+H9</f>
-        <v>1.5</v>
+        <f t="shared" si="0"/>
+        <v>1.35</v>
       </c>
       <c r="E9" s="4">
-        <v>1.1499999999999999</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4">
@@ -1544,16 +1478,16 @@
     </row>
     <row r="10" spans="1:8" ht="18.75">
       <c r="A10" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>62</v>
       </c>
       <c r="D10" s="8">
-        <f>F10+G10+H10</f>
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="E10" s="4">
@@ -1569,226 +1503,226 @@
     </row>
     <row r="11" spans="1:8" ht="18.75">
       <c r="A11" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>62</v>
       </c>
       <c r="D11" s="8">
-        <f>F11+G11+H11</f>
-        <v>1.35</v>
+        <f t="shared" si="0"/>
+        <v>1.5</v>
       </c>
       <c r="E11" s="4">
         <v>1.1499999999999999</v>
       </c>
       <c r="F11" s="4">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="18.75">
       <c r="A12" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>62</v>
       </c>
       <c r="D12" s="8">
-        <f>F12+G12+H12</f>
-        <v>1.78</v>
+        <f t="shared" si="0"/>
+        <v>1.35</v>
       </c>
       <c r="E12" s="4">
-        <v>1.45</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="F12" s="4">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4">
-        <v>1.25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="18.75">
       <c r="A13" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D13" s="8">
-        <f>F13+G13+H13</f>
-        <v>1.5</v>
+        <f t="shared" si="0"/>
+        <v>1.78</v>
       </c>
       <c r="E13" s="4">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="F13" s="4">
-        <v>1</v>
+        <v>0.53</v>
       </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18.75">
+      <c r="A14" s="8">
+        <v>10</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" s="8">
+        <f t="shared" si="0"/>
+        <v>1.5</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1.5</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="18.75">
-      <c r="A14" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8">
-        <f>F14+G14+H14</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" ht="18.75">
       <c r="A15" s="6" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="D15" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" ht="18.75">
-      <c r="A16" s="8">
-        <v>1</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="8">
-        <f>F16+G16+H16</f>
-        <v>19</v>
-      </c>
-      <c r="E16" s="4">
-        <v>7</v>
-      </c>
-      <c r="F16" s="4">
-        <v>5</v>
-      </c>
-      <c r="G16" s="4">
-        <v>5</v>
-      </c>
-      <c r="H16" s="4">
-        <v>9</v>
-      </c>
+      <c r="A16" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="18.75">
       <c r="A17" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C17" s="8" t="s">
         <v>51</v>
       </c>
       <c r="D17" s="8">
-        <f>F17+G17+H17</f>
-        <v>4</v>
+        <f t="shared" si="0"/>
+        <v>19</v>
       </c>
       <c r="E17" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F17" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G17" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17" s="4">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="18.75">
       <c r="A18" s="8">
+        <v>2</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="8">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E18" s="4">
         <v>3</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="8">
-        <f>F18+G18+H18</f>
-        <v>22</v>
-      </c>
-      <c r="E18" s="4">
-        <v>13</v>
-      </c>
       <c r="F18" s="4">
-        <v>8</v>
-      </c>
-      <c r="G18" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
       <c r="H18" s="4">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="18.75">
       <c r="A19" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="8">
-        <f>F19+G19+H19</f>
-        <v>105</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
       <c r="E19" s="4">
-        <v>105</v>
+        <v>13</v>
       </c>
       <c r="F19" s="4">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="G19" s="4"/>
       <c r="H19" s="4">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="18.75">
       <c r="A20" s="8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D20" s="8">
-        <f>F20+G20+H20</f>
+        <f t="shared" si="0"/>
         <v>105</v>
       </c>
       <c r="E20" s="4">
@@ -1803,196 +1737,370 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="18.75">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="8">
+        <v>5</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="8">
+        <f t="shared" si="0"/>
+        <v>105</v>
+      </c>
+      <c r="E21" s="4">
+        <v>105</v>
+      </c>
+      <c r="F21" s="4">
+        <v>100</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="18.75">
+      <c r="A22" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B22" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="1:8" ht="18.75">
-      <c r="A22" s="8">
-        <v>7</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22" s="8">
-        <f>F22+G22+H22</f>
-        <v>14</v>
-      </c>
-      <c r="E22" s="4">
-        <v>4</v>
-      </c>
-      <c r="F22" s="4">
-        <v>2</v>
-      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="4">
-        <v>12</v>
-      </c>
+      <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" ht="18.75">
       <c r="A23" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="D23" s="8">
-        <f>F23+G23+H23</f>
-        <v>32</v>
+        <f t="shared" si="0"/>
+        <v>14</v>
       </c>
       <c r="E23" s="4">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F23" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="18.75">
       <c r="A24" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D24" s="8">
-        <f>F24+G24+H24</f>
-        <v>43</v>
+        <f t="shared" si="0"/>
+        <v>32</v>
       </c>
       <c r="E24" s="4">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F24" s="4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G24" s="4"/>
       <c r="H24" s="4">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="18.75">
       <c r="A25" s="8">
+        <v>9</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="8">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="E25" s="4">
+        <v>24</v>
+      </c>
+      <c r="F25" s="4">
         <v>10</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" s="8">
-        <f>F25+G25+H25</f>
-        <v>3</v>
-      </c>
-      <c r="E25" s="4">
-        <v>2</v>
-      </c>
-      <c r="F25" s="4">
-        <v>2</v>
       </c>
       <c r="G25" s="4"/>
       <c r="H25" s="4">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="18.75">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="8">
+        <v>10</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="E26" s="4">
+        <v>2</v>
+      </c>
+      <c r="F26" s="4">
+        <v>2</v>
+      </c>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="18.75">
+      <c r="A27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B27" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="1:8" ht="18.75">
-      <c r="A27" s="8">
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+    </row>
+    <row r="28" spans="1:8" ht="18.75">
+      <c r="A28" s="8">
         <v>12</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B28" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C28" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="8">
-        <f>F27+G27+H27</f>
+      <c r="D28" s="8">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="E27" s="4">
+      <c r="E28" s="4">
         <v>7</v>
       </c>
-      <c r="F27" s="4">
+      <c r="F28" s="4">
         <v>5</v>
       </c>
-      <c r="G27" s="4">
+      <c r="G28" s="4">
         <v>5</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H28" s="4">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="18.75">
-      <c r="A28" s="6" t="s">
+    <row r="29" spans="1:8" ht="18.75">
+      <c r="A29" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B29" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C29" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="8">
-        <f>F28+G28+H28</f>
+      <c r="D29" s="8">
+        <f t="shared" si="0"/>
         <v>1.1000000000000001</v>
       </c>
-      <c r="E28" s="4">
-        <v>1</v>
-      </c>
-      <c r="F28" s="4">
+      <c r="E29" s="4">
+        <v>1</v>
+      </c>
+      <c r="F29" s="4">
         <v>0.5</v>
       </c>
-      <c r="G28" s="4">
+      <c r="G29" s="4">
         <v>0.1</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H29" s="4">
         <v>0.5</v>
       </c>
     </row>
+    <row r="30" spans="1:8" ht="18.75">
+      <c r="A30" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="10"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+    </row>
+    <row r="31" spans="1:8" ht="18.75">
+      <c r="A31" s="13"/>
+      <c r="B31" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="12">
+        <v>20</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+    </row>
+    <row r="32" spans="1:8" ht="37.5">
+      <c r="A32" s="13"/>
+      <c r="B32" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+    </row>
+    <row r="33" spans="1:8" ht="18.75">
+      <c r="A33" s="13"/>
+      <c r="B33" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="12">
+        <v>8</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+    </row>
+    <row r="34" spans="1:8" ht="18.75">
+      <c r="A34" s="13"/>
+      <c r="B34" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C34" s="12">
+        <v>50</v>
+      </c>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+    </row>
+    <row r="35" spans="1:8" ht="18.75">
+      <c r="A35" s="13"/>
+      <c r="B35" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="12">
+        <v>1.5</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+    </row>
+    <row r="36" spans="1:8" ht="18.75">
+      <c r="A36" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="13"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" spans="1:8" ht="18.75">
+      <c r="A37" s="13"/>
+      <c r="B37" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="12">
+        <v>8</v>
+      </c>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+    </row>
+    <row r="38" spans="1:8" ht="18.75">
+      <c r="A38" s="13"/>
+      <c r="B38" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="12">
+        <v>7.5</v>
+      </c>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+    </row>
+    <row r="39" spans="1:8" ht="18.75">
+      <c r="A39" s="13"/>
+      <c r="B39" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="12">
+        <v>9</v>
+      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+    </row>
+    <row r="40" spans="1:8" ht="18.75">
+      <c r="A40" s="13"/>
+      <c r="B40" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="12">
+        <v>2</v>
+      </c>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Resources/Sheet/TinhHinhDonVi.xlsx
+++ b/Resources/Sheet/TinhHinhDonVi.xlsx
@@ -5,17 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\BODOIAPP\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codenew\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D5D8C40-7295-4B1C-B903-1A5D186BF23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941150DC-785B-4588-AF45-22A9EB7688A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TinhHinhVc" sheetId="15" r:id="rId1"/>
     <sheet name="ChiLenhHCKT" sheetId="14" r:id="rId2"/>
-    <sheet name="KeHoachDuKien" sheetId="16" r:id="rId3"/>
+    <sheet name="ToChucLucLuong" sheetId="17" r:id="rId3"/>
+    <sheet name="KeHoachDuKien" sheetId="16" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="115">
   <si>
     <t>Lựu đạn</t>
   </si>
@@ -296,18 +297,109 @@
   </si>
   <si>
     <t>1. Quy định dự trữ, tiêu thụ, bổ sung vật chất</t>
+  </si>
+  <si>
+    <t>Nội dung</t>
+  </si>
+  <si>
+    <t>Quân số</t>
+  </si>
+  <si>
+    <t>Vũ khí trang bị kỹ thuật</t>
+  </si>
+  <si>
+    <t>Phân chia lực lượng</t>
+  </si>
+  <si>
+    <t>SQ</t>
+  </si>
+  <si>
+    <t>QNCN</t>
+  </si>
+  <si>
+    <t>HSQ-BS</t>
+  </si>
+  <si>
+    <t>Vũ khí</t>
+  </si>
+  <si>
+    <t>Xe-máy</t>
+  </si>
+  <si>
+    <t>TB khác</t>
+  </si>
+  <si>
+    <t>Bộ phận HC-KT</t>
+  </si>
+  <si>
+    <t>Lực lượng tăng cường cho đơn vị</t>
+  </si>
+  <si>
+    <t>QS</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>Phân đội HC-KT</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>TLHC/d</t>
+  </si>
+  <si>
+    <t>NVQK</t>
+  </si>
+  <si>
+    <t>NVQN</t>
+  </si>
+  <si>
+    <t>NVKT</t>
+  </si>
+  <si>
+    <t>QY/d</t>
+  </si>
+  <si>
+    <t>bVTB/d</t>
+  </si>
+  <si>
+    <t>bPV/d</t>
+  </si>
+  <si>
+    <t>LL tăng cường</t>
+  </si>
+  <si>
+    <t>QY/e</t>
+  </si>
+  <si>
+    <t>bVTB/e</t>
+  </si>
+  <si>
+    <t>Tổ SC/e</t>
+  </si>
+  <si>
+    <t>Cộng</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -323,8 +415,16 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -343,8 +443,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -367,31 +473,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -400,20 +524,83 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -699,28 +886,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="18.75">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
       <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
@@ -730,7 +917,7 @@
       <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="34"/>
     </row>
     <row r="3" spans="1:7" ht="18.75">
       <c r="A3" s="1" t="s">
@@ -1288,48 +1475,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="35" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="18.75">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="F2" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="H2" s="17"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" spans="1:8" ht="37.5">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="A3" s="36"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
       <c r="G3" s="6" t="s">
         <v>11</v>
       </c>
@@ -1944,9 +2131,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="18.75">
-      <c r="A30" s="10" t="s">
-        <v>77</v>
-      </c>
+      <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="11"/>
       <c r="D30" s="12"/>
@@ -1957,23 +2142,17 @@
     </row>
     <row r="31" spans="1:8" ht="18.75">
       <c r="A31" s="13"/>
-      <c r="B31" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="12">
-        <v>20</v>
-      </c>
+      <c r="B31" s="14"/>
+      <c r="C31" s="12"/>
       <c r="D31" s="12"/>
       <c r="E31" s="12"/>
       <c r="F31" s="12"/>
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
     </row>
-    <row r="32" spans="1:8" ht="37.5">
+    <row r="32" spans="1:8" ht="18.75">
       <c r="A32" s="13"/>
-      <c r="B32" s="14" t="s">
-        <v>79</v>
-      </c>
+      <c r="B32" s="14"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
       <c r="E32" s="12"/>
@@ -1983,12 +2162,8 @@
     </row>
     <row r="33" spans="1:8" ht="18.75">
       <c r="A33" s="13"/>
-      <c r="B33" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="12">
-        <v>8</v>
-      </c>
+      <c r="B33" s="14"/>
+      <c r="C33" s="12"/>
       <c r="D33" s="12"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12"/>
@@ -1997,12 +2172,8 @@
     </row>
     <row r="34" spans="1:8" ht="18.75">
       <c r="A34" s="13"/>
-      <c r="B34" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C34" s="12">
-        <v>50</v>
-      </c>
+      <c r="B34" s="14"/>
+      <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="12"/>
       <c r="F34" s="12"/>
@@ -2011,12 +2182,8 @@
     </row>
     <row r="35" spans="1:8" ht="18.75">
       <c r="A35" s="13"/>
-      <c r="B35" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" s="12">
-        <v>1.5</v>
-      </c>
+      <c r="B35" s="14"/>
+      <c r="C35" s="12"/>
       <c r="D35" s="12"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12"/>
@@ -2024,9 +2191,7 @@
       <c r="H35" s="12"/>
     </row>
     <row r="36" spans="1:8" ht="18.75">
-      <c r="A36" s="10" t="s">
-        <v>83</v>
-      </c>
+      <c r="A36" s="10"/>
       <c r="B36" s="13"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -2037,12 +2202,8 @@
     </row>
     <row r="37" spans="1:8" ht="18.75">
       <c r="A37" s="13"/>
-      <c r="B37" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="12">
-        <v>8</v>
-      </c>
+      <c r="B37" s="14"/>
+      <c r="C37" s="12"/>
       <c r="D37" s="12"/>
       <c r="E37" s="12"/>
       <c r="F37" s="12"/>
@@ -2051,12 +2212,8 @@
     </row>
     <row r="38" spans="1:8" ht="18.75">
       <c r="A38" s="13"/>
-      <c r="B38" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="12">
-        <v>7.5</v>
-      </c>
+      <c r="B38" s="14"/>
+      <c r="C38" s="12"/>
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
       <c r="F38" s="12"/>
@@ -2065,12 +2222,8 @@
     </row>
     <row r="39" spans="1:8" ht="18.75">
       <c r="A39" s="13"/>
-      <c r="B39" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="12">
-        <v>9</v>
-      </c>
+      <c r="B39" s="14"/>
+      <c r="C39" s="12"/>
       <c r="D39" s="12"/>
       <c r="E39" s="12"/>
       <c r="F39" s="12"/>
@@ -2079,12 +2232,8 @@
     </row>
     <row r="40" spans="1:8" ht="18.75">
       <c r="A40" s="13"/>
-      <c r="B40" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="C40" s="12">
-        <v>2</v>
-      </c>
+      <c r="B40" s="14"/>
+      <c r="C40" s="12"/>
       <c r="D40" s="12"/>
       <c r="E40" s="12"/>
       <c r="F40" s="12"/>
@@ -2108,6 +2257,525 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18876574-07EF-43D9-A34F-295A991584F3}">
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="37"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="K2" s="37"/>
+      <c r="L2" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="M2" s="38"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="37"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="37"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
+      <c r="I4" s="37"/>
+      <c r="J4" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="15">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C5" s="15">
+        <f>SUM(C6:C12)</f>
+        <v>2</v>
+      </c>
+      <c r="D5" s="15">
+        <f>SUM(D6:D12)</f>
+        <v>5</v>
+      </c>
+      <c r="E5" s="15">
+        <f>SUM(E6:E12)</f>
+        <v>54</v>
+      </c>
+      <c r="F5" s="15">
+        <f>SUM(F6:F12)</f>
+        <v>61</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="15">
+        <v>1</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15">
+        <f t="shared" ref="F6:F12" si="0">SUM(C6:E6)</f>
+        <v>1</v>
+      </c>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15">
+        <v>1</v>
+      </c>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15">
+        <v>2</v>
+      </c>
+      <c r="F10" s="15">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+      <c r="M10" s="17"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" s="15">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15">
+        <v>27</v>
+      </c>
+      <c r="F11" s="15">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+      <c r="M11" s="17"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22">
+        <v>1</v>
+      </c>
+      <c r="E12" s="22">
+        <v>25</v>
+      </c>
+      <c r="F12" s="15">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="15">
+        <v>2</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="15">
+        <f>C14+C15+C16</f>
+        <v>1</v>
+      </c>
+      <c r="D13" s="15">
+        <f>D14+D15+D16</f>
+        <v>4</v>
+      </c>
+      <c r="E13" s="15">
+        <f>E14+E15+E16</f>
+        <v>29</v>
+      </c>
+      <c r="F13" s="15">
+        <f>F14+F15+F16</f>
+        <v>34</v>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17">
+        <v>1</v>
+      </c>
+      <c r="E14" s="17">
+        <v>2</v>
+      </c>
+      <c r="F14" s="15">
+        <f>SUM(C14:E14)</f>
+        <v>3</v>
+      </c>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="28">
+        <v>1</v>
+      </c>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28">
+        <v>27</v>
+      </c>
+      <c r="F15" s="15">
+        <f>SUM(C15:E15)</f>
+        <v>28</v>
+      </c>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28">
+        <v>3</v>
+      </c>
+      <c r="E16" s="28"/>
+      <c r="F16" s="15">
+        <f>SUM(C16:E16)</f>
+        <v>3</v>
+      </c>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="30"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="15">
+        <f t="shared" ref="F17:F18" si="1">SUM(C17:E17)</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="30"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="31"/>
+      <c r="C19" s="32">
+        <f>C13+C5</f>
+        <v>3</v>
+      </c>
+      <c r="D19" s="32">
+        <f t="shared" ref="D19:F19" si="2">D13+D5</f>
+        <v>9</v>
+      </c>
+      <c r="E19" s="32">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="F19" s="32">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="32">
+        <f>J13+J5</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="32">
+        <f>K13+K5</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="32">
+        <f>L13+L5</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="32">
+        <f>M13+M5</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:K3"/>
+    <mergeCell ref="L2:M3"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="F2:F4"/>
+    <mergeCell ref="G2:G4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5011F223-0C6D-4F39-9B4C-A9EA28CB4875}">
   <dimension ref="A2:H12"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/Resources/Sheet/TinhHinhDonVi.xlsx
+++ b/Resources/Sheet/TinhHinhDonVi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codenew\Resources\Sheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\BODOIAPP\Resources\Sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941150DC-785B-4588-AF45-22A9EB7688A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47917D68-4486-47D2-A4E1-D4AE88C12424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TinhHinhVc" sheetId="15" r:id="rId1"/>
@@ -879,13 +879,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FDDA00E-0AB1-47FB-A67C-16A3EB46124C}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="33.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="33.6640625" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75">
+    <row r="1" spans="1:7" ht="17.399999999999999">
       <c r="A1" s="34" t="s">
         <v>2</v>
       </c>
@@ -904,7 +904,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75">
+    <row r="2" spans="1:7" ht="17.399999999999999">
       <c r="A2" s="34"/>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -919,7 +919,7 @@
       </c>
       <c r="G2" s="34"/>
     </row>
-    <row r="3" spans="1:7" ht="18.75">
+    <row r="3" spans="1:7" ht="18">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -932,7 +932,7 @@
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:7" ht="18.75">
+    <row r="4" spans="1:7" ht="18">
       <c r="A4" s="3">
         <v>1</v>
       </c>
@@ -942,19 +942,15 @@
       <c r="C4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1</v>
-      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
       <c r="F4" s="4">
         <f>D4+E4</f>
-        <v>1.1499999999999999</v>
+        <v>0</v>
       </c>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="18.75">
+    <row r="5" spans="1:7" ht="18">
       <c r="A5" s="3">
         <v>2</v>
       </c>
@@ -964,19 +960,15 @@
       <c r="C5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0.5</v>
-      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
       <c r="F5" s="4">
         <f t="shared" ref="F5:F29" si="0">D5+E5</f>
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="18.75">
+    <row r="6" spans="1:7" ht="18">
       <c r="A6" s="3">
         <v>3</v>
       </c>
@@ -986,19 +978,15 @@
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0.5</v>
-      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
       <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="18.75">
+    <row r="7" spans="1:7" ht="18">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1008,19 +996,15 @@
       <c r="C7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="E7" s="4">
-        <v>0.33</v>
-      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
       <c r="F7" s="4">
         <f t="shared" si="0"/>
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="18.75">
+    <row r="8" spans="1:7" ht="18">
       <c r="A8" s="3">
         <v>5</v>
       </c>
@@ -1030,19 +1014,15 @@
       <c r="C8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="E8" s="4">
-        <v>0.2</v>
-      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
       <c r="F8" s="4">
         <f t="shared" si="0"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="18.75">
+    <row r="9" spans="1:7" ht="18">
       <c r="A9" s="3">
         <v>6</v>
       </c>
@@ -1052,19 +1032,15 @@
       <c r="C9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="E9" s="4">
-        <v>0.1</v>
-      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="4">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="18.75">
+    <row r="10" spans="1:7" ht="18">
       <c r="A10" s="3">
         <v>7</v>
       </c>
@@ -1074,19 +1050,15 @@
       <c r="C10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0.1</v>
-      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="4">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="18.75">
+    <row r="11" spans="1:7" ht="18">
       <c r="A11" s="3">
         <v>8</v>
       </c>
@@ -1096,18 +1068,14 @@
       <c r="C11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="4">
-        <v>0</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="4">
         <v>0</v>
       </c>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="18.75">
+    <row r="12" spans="1:7" ht="18">
       <c r="A12" s="3">
         <v>9</v>
       </c>
@@ -1117,19 +1085,15 @@
       <c r="C12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D12" s="4">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0.3</v>
-      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="4">
         <f t="shared" si="0"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" ht="18.75">
+    <row r="13" spans="1:7" ht="18">
       <c r="A13" s="3">
         <v>10</v>
       </c>
@@ -1139,19 +1103,15 @@
       <c r="C13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="E13" s="4">
-        <v>1</v>
-      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
       <c r="F13" s="4">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
+        <v>0</v>
       </c>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7" ht="18.75">
+    <row r="14" spans="1:7" ht="18">
       <c r="A14" s="1" t="s">
         <v>5</v>
       </c>
@@ -1164,7 +1124,7 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7" ht="18.75">
+    <row r="15" spans="1:7" ht="18">
       <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
@@ -1177,7 +1137,7 @@
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="1:7" ht="18.75">
+    <row r="16" spans="1:7" ht="18">
       <c r="A16" s="3">
         <v>1</v>
       </c>
@@ -1187,19 +1147,15 @@
       <c r="C16" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="4">
-        <v>2</v>
-      </c>
-      <c r="E16" s="4">
-        <v>3</v>
-      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
       <c r="F16" s="4">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="1:7" ht="18.75">
+    <row r="17" spans="1:7" ht="18">
       <c r="A17" s="3">
         <v>2</v>
       </c>
@@ -1209,19 +1165,15 @@
       <c r="C17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4">
-        <v>1</v>
-      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
       <c r="F17" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="1:7" ht="18.75">
+    <row r="18" spans="1:7" ht="18">
       <c r="A18" s="3">
         <v>3</v>
       </c>
@@ -1231,19 +1183,15 @@
       <c r="C18" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4">
-        <v>1</v>
-      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
       <c r="F18" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="1:7" ht="18.75">
+    <row r="19" spans="1:7" ht="18">
       <c r="A19" s="3">
         <v>4</v>
       </c>
@@ -1254,16 +1202,14 @@
         <v>3</v>
       </c>
       <c r="D19" s="4"/>
-      <c r="E19" s="4">
-        <v>100</v>
-      </c>
+      <c r="E19" s="4"/>
       <c r="F19" s="4">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:7" ht="18.75">
+    <row r="20" spans="1:7" ht="18">
       <c r="A20" s="3">
         <v>5</v>
       </c>
@@ -1274,16 +1220,14 @@
         <v>22</v>
       </c>
       <c r="D20" s="4"/>
-      <c r="E20" s="4">
-        <v>100</v>
-      </c>
+      <c r="E20" s="4"/>
       <c r="F20" s="4">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="1:7" ht="18.75">
+    <row r="21" spans="1:7" ht="18">
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
@@ -1296,7 +1240,7 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="1:7" ht="18.75">
+    <row r="22" spans="1:7" ht="18">
       <c r="A22" s="3">
         <v>6</v>
       </c>
@@ -1306,19 +1250,15 @@
       <c r="C22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4">
-        <v>1</v>
-      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
       <c r="F22" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="1:7" ht="18.75">
+    <row r="23" spans="1:7" ht="18">
       <c r="A23" s="3">
         <v>7</v>
       </c>
@@ -1328,19 +1268,15 @@
       <c r="C23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="4">
-        <v>2</v>
-      </c>
-      <c r="E23" s="4">
-        <v>5</v>
-      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
       <c r="F23" s="4">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="1:7" ht="18.75">
+    <row r="24" spans="1:7" ht="18">
       <c r="A24" s="3">
         <v>8</v>
       </c>
@@ -1350,19 +1286,15 @@
       <c r="C24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="4">
-        <v>8</v>
-      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
       <c r="F24" s="4">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="1:7" ht="18.75">
+    <row r="25" spans="1:7" ht="18">
       <c r="A25" s="3">
         <v>9</v>
       </c>
@@ -1373,16 +1305,14 @@
         <v>47</v>
       </c>
       <c r="D25" s="4"/>
-      <c r="E25" s="4">
-        <v>1</v>
-      </c>
+      <c r="E25" s="4"/>
       <c r="F25" s="4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="1:7" ht="18.75">
+    <row r="26" spans="1:7" ht="18">
       <c r="A26" s="1" t="s">
         <v>48</v>
       </c>
@@ -1395,7 +1325,7 @@
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
     </row>
-    <row r="27" spans="1:7" ht="18.75">
+    <row r="27" spans="1:7" ht="18">
       <c r="A27" s="3">
         <v>10</v>
       </c>
@@ -1405,19 +1335,15 @@
       <c r="C27" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="4">
-        <v>2</v>
-      </c>
-      <c r="E27" s="4">
-        <v>3</v>
-      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
       <c r="F27" s="4">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4"/>
     </row>
-    <row r="28" spans="1:7" ht="18.75">
+    <row r="28" spans="1:7" ht="18">
       <c r="A28" s="1" t="s">
         <v>52</v>
       </c>
@@ -1430,7 +1356,7 @@
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
     </row>
-    <row r="29" spans="1:7" ht="18.75">
+    <row r="29" spans="1:7" ht="18">
       <c r="A29" s="3">
         <v>1</v>
       </c>
@@ -1440,15 +1366,11 @@
       <c r="C29" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D29" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="E29" s="4">
-        <v>0.1</v>
-      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="4">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="4"/>
     </row>
@@ -1467,14 +1389,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB73341-358E-4E08-B0AC-7C6EA0655E0C}">
   <dimension ref="A1:H40"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="43.33203125" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75">
+    <row r="1" spans="1:8" ht="17.399999999999999">
       <c r="A1" s="35" t="s">
         <v>86</v>
       </c>
@@ -1486,7 +1408,7 @@
       <c r="G1" s="35"/>
       <c r="H1" s="35"/>
     </row>
-    <row r="2" spans="1:8" ht="18.75">
+    <row r="2" spans="1:8" ht="17.399999999999999">
       <c r="A2" s="36" t="s">
         <v>2</v>
       </c>
@@ -1510,7 +1432,7 @@
       </c>
       <c r="H2" s="36"/>
     </row>
-    <row r="3" spans="1:8" ht="37.5">
+    <row r="3" spans="1:8" ht="17.399999999999999">
       <c r="A3" s="36"/>
       <c r="B3" s="36"/>
       <c r="C3" s="36"/>
@@ -1524,7 +1446,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75">
+    <row r="4" spans="1:8" ht="18">
       <c r="A4" s="6" t="s">
         <v>4</v>
       </c>
@@ -1538,7 +1460,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" ht="18.75">
+    <row r="5" spans="1:8" ht="18">
       <c r="A5" s="8">
         <v>1</v>
       </c>
@@ -1550,20 +1472,14 @@
       </c>
       <c r="D5" s="8">
         <f>F5+G5+H5</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E5" s="4">
-        <v>1.45</v>
-      </c>
-      <c r="F5" s="4">
-        <v>1.2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18.75">
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="18">
       <c r="A6" s="8">
         <v>2</v>
       </c>
@@ -1575,20 +1491,14 @@
       </c>
       <c r="D6" s="8">
         <f t="shared" ref="D6:D29" si="0">F6+G6+H6</f>
-        <v>1.7</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1.45</v>
-      </c>
-      <c r="F6" s="4">
-        <v>0.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18.75">
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" ht="18">
       <c r="A7" s="8">
         <v>3</v>
       </c>
@@ -1600,20 +1510,14 @@
       </c>
       <c r="D7" s="8">
         <f t="shared" si="0"/>
-        <v>1.7</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1.45</v>
-      </c>
-      <c r="F7" s="4">
-        <v>0.7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="18.75">
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" ht="18">
       <c r="A8" s="8">
         <v>4</v>
       </c>
@@ -1625,20 +1529,14 @@
       </c>
       <c r="D8" s="8">
         <f t="shared" si="0"/>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1.75</v>
-      </c>
-      <c r="F8" s="4">
-        <v>0.8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="4">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18.75">
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" ht="18">
       <c r="A9" s="8">
         <v>5</v>
       </c>
@@ -1650,20 +1548,14 @@
       </c>
       <c r="D9" s="8">
         <f t="shared" si="0"/>
-        <v>1.35</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0.1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="18.75">
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" ht="18">
       <c r="A10" s="8">
         <v>6</v>
       </c>
@@ -1675,20 +1567,14 @@
       </c>
       <c r="D10" s="8">
         <f t="shared" si="0"/>
-        <v>1.5</v>
-      </c>
-      <c r="E10" s="4">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="F10" s="4">
-        <v>0.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="18.75">
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" ht="18">
       <c r="A11" s="8">
         <v>7</v>
       </c>
@@ -1700,20 +1586,14 @@
       </c>
       <c r="D11" s="8">
         <f t="shared" si="0"/>
-        <v>1.5</v>
-      </c>
-      <c r="E11" s="4">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="F11" s="4">
-        <v>0.25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="18.75">
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" ht="18">
       <c r="A12" s="8">
         <v>8</v>
       </c>
@@ -1725,20 +1605,14 @@
       </c>
       <c r="D12" s="8">
         <f t="shared" si="0"/>
-        <v>1.35</v>
-      </c>
-      <c r="E12" s="4">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0.35</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="18.75">
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="18">
       <c r="A13" s="8">
         <v>9</v>
       </c>
@@ -1750,20 +1624,14 @@
       </c>
       <c r="D13" s="8">
         <f t="shared" si="0"/>
-        <v>1.78</v>
-      </c>
-      <c r="E13" s="4">
-        <v>1.45</v>
-      </c>
-      <c r="F13" s="4">
-        <v>0.53</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="4">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="18.75">
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" ht="18">
       <c r="A14" s="8">
         <v>10</v>
       </c>
@@ -1775,20 +1643,14 @@
       </c>
       <c r="D14" s="8">
         <f t="shared" si="0"/>
-        <v>1.5</v>
-      </c>
-      <c r="E14" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="18.75">
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" ht="18">
       <c r="A15" s="6" t="s">
         <v>5</v>
       </c>
@@ -1805,7 +1667,7 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:8" ht="18.75">
+    <row r="16" spans="1:8" ht="18">
       <c r="A16" s="6" t="s">
         <v>31</v>
       </c>
@@ -1819,7 +1681,7 @@
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
     </row>
-    <row r="17" spans="1:8" ht="18.75">
+    <row r="17" spans="1:8" ht="18">
       <c r="A17" s="8">
         <v>1</v>
       </c>
@@ -1831,22 +1693,14 @@
       </c>
       <c r="D17" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="E17" s="4">
-        <v>7</v>
-      </c>
-      <c r="F17" s="4">
-        <v>5</v>
-      </c>
-      <c r="G17" s="4">
-        <v>5</v>
-      </c>
-      <c r="H17" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="18.75">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" ht="18">
       <c r="A18" s="8">
         <v>2</v>
       </c>
@@ -1858,22 +1712,14 @@
       </c>
       <c r="D18" s="8">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E18" s="4">
-        <v>3</v>
-      </c>
-      <c r="F18" s="4">
-        <v>2</v>
-      </c>
-      <c r="G18" s="4">
-        <v>0</v>
-      </c>
-      <c r="H18" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="18.75">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" ht="18">
       <c r="A19" s="8">
         <v>3</v>
       </c>
@@ -1885,20 +1731,14 @@
       </c>
       <c r="D19" s="8">
         <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="E19" s="4">
-        <v>13</v>
-      </c>
-      <c r="F19" s="4">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="4">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="18.75">
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" ht="18">
       <c r="A20" s="8">
         <v>4</v>
       </c>
@@ -1910,20 +1750,14 @@
       </c>
       <c r="D20" s="8">
         <f t="shared" si="0"/>
-        <v>105</v>
-      </c>
-      <c r="E20" s="4">
-        <v>105</v>
-      </c>
-      <c r="F20" s="4">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
       <c r="G20" s="4"/>
-      <c r="H20" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="18.75">
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" ht="18">
       <c r="A21" s="8">
         <v>5</v>
       </c>
@@ -1935,20 +1769,14 @@
       </c>
       <c r="D21" s="8">
         <f t="shared" si="0"/>
-        <v>105</v>
-      </c>
-      <c r="E21" s="4">
-        <v>105</v>
-      </c>
-      <c r="F21" s="4">
-        <v>100</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="18.75">
+      <c r="H21" s="4"/>
+    </row>
+    <row r="22" spans="1:8" ht="18">
       <c r="A22" s="6" t="s">
         <v>40</v>
       </c>
@@ -1962,7 +1790,7 @@
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
     </row>
-    <row r="23" spans="1:8" ht="18.75">
+    <row r="23" spans="1:8" ht="18">
       <c r="A23" s="8">
         <v>7</v>
       </c>
@@ -1974,20 +1802,14 @@
       </c>
       <c r="D23" s="8">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="E23" s="4">
-        <v>4</v>
-      </c>
-      <c r="F23" s="4">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="4">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="18.75">
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" ht="18">
       <c r="A24" s="8">
         <v>8</v>
       </c>
@@ -1999,20 +1821,14 @@
       </c>
       <c r="D24" s="8">
         <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="E24" s="4">
-        <v>18</v>
-      </c>
-      <c r="F24" s="4">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="18.75">
+      <c r="H24" s="4"/>
+    </row>
+    <row r="25" spans="1:8" ht="18">
       <c r="A25" s="8">
         <v>9</v>
       </c>
@@ -2024,20 +1840,14 @@
       </c>
       <c r="D25" s="8">
         <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="E25" s="4">
-        <v>24</v>
-      </c>
-      <c r="F25" s="4">
-        <v>10</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="4">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="18.75">
+      <c r="H25" s="4"/>
+    </row>
+    <row r="26" spans="1:8" ht="18">
       <c r="A26" s="8">
         <v>10</v>
       </c>
@@ -2049,20 +1859,14 @@
       </c>
       <c r="D26" s="8">
         <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="E26" s="4">
-        <v>2</v>
-      </c>
-      <c r="F26" s="4">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="18.75">
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" ht="18">
       <c r="A27" s="6" t="s">
         <v>40</v>
       </c>
@@ -2076,7 +1880,7 @@
       <c r="G27" s="4"/>
       <c r="H27" s="4"/>
     </row>
-    <row r="28" spans="1:8" ht="18.75">
+    <row r="28" spans="1:8" ht="18">
       <c r="A28" s="8">
         <v>12</v>
       </c>
@@ -2088,22 +1892,14 @@
       </c>
       <c r="D28" s="8">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="E28" s="4">
-        <v>7</v>
-      </c>
-      <c r="F28" s="4">
-        <v>5</v>
-      </c>
-      <c r="G28" s="4">
-        <v>5</v>
-      </c>
-      <c r="H28" s="4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="18.75">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+    </row>
+    <row r="29" spans="1:8" ht="18">
       <c r="A29" s="6" t="s">
         <v>52</v>
       </c>
@@ -2115,22 +1911,14 @@
       </c>
       <c r="D29" s="8">
         <f t="shared" si="0"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="E29" s="4">
-        <v>1</v>
-      </c>
-      <c r="F29" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="G29" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="H29" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="18.75">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+    </row>
+    <row r="30" spans="1:8" ht="18">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="11"/>
@@ -2140,7 +1928,7 @@
       <c r="G30" s="12"/>
       <c r="H30" s="12"/>
     </row>
-    <row r="31" spans="1:8" ht="18.75">
+    <row r="31" spans="1:8" ht="18">
       <c r="A31" s="13"/>
       <c r="B31" s="14"/>
       <c r="C31" s="12"/>
@@ -2150,7 +1938,7 @@
       <c r="G31" s="12"/>
       <c r="H31" s="12"/>
     </row>
-    <row r="32" spans="1:8" ht="18.75">
+    <row r="32" spans="1:8" ht="18">
       <c r="A32" s="13"/>
       <c r="B32" s="14"/>
       <c r="C32" s="12"/>
@@ -2160,7 +1948,7 @@
       <c r="G32" s="12"/>
       <c r="H32" s="12"/>
     </row>
-    <row r="33" spans="1:8" ht="18.75">
+    <row r="33" spans="1:8" ht="18">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="12"/>
@@ -2170,7 +1958,7 @@
       <c r="G33" s="12"/>
       <c r="H33" s="12"/>
     </row>
-    <row r="34" spans="1:8" ht="18.75">
+    <row r="34" spans="1:8" ht="18">
       <c r="A34" s="13"/>
       <c r="B34" s="14"/>
       <c r="C34" s="12"/>
@@ -2180,7 +1968,7 @@
       <c r="G34" s="12"/>
       <c r="H34" s="12"/>
     </row>
-    <row r="35" spans="1:8" ht="18.75">
+    <row r="35" spans="1:8" ht="18">
       <c r="A35" s="13"/>
       <c r="B35" s="14"/>
       <c r="C35" s="12"/>
@@ -2190,7 +1978,7 @@
       <c r="G35" s="12"/>
       <c r="H35" s="12"/>
     </row>
-    <row r="36" spans="1:8" ht="18.75">
+    <row r="36" spans="1:8" ht="18">
       <c r="A36" s="10"/>
       <c r="B36" s="13"/>
       <c r="C36" s="12"/>
@@ -2200,7 +1988,7 @@
       <c r="G36" s="12"/>
       <c r="H36" s="12"/>
     </row>
-    <row r="37" spans="1:8" ht="18.75">
+    <row r="37" spans="1:8" ht="18">
       <c r="A37" s="13"/>
       <c r="B37" s="14"/>
       <c r="C37" s="12"/>
@@ -2210,7 +1998,7 @@
       <c r="G37" s="12"/>
       <c r="H37" s="12"/>
     </row>
-    <row r="38" spans="1:8" ht="18.75">
+    <row r="38" spans="1:8" ht="18">
       <c r="A38" s="13"/>
       <c r="B38" s="14"/>
       <c r="C38" s="12"/>
@@ -2220,7 +2008,7 @@
       <c r="G38" s="12"/>
       <c r="H38" s="12"/>
     </row>
-    <row r="39" spans="1:8" ht="18.75">
+    <row r="39" spans="1:8" ht="18">
       <c r="A39" s="13"/>
       <c r="B39" s="14"/>
       <c r="C39" s="12"/>
@@ -2230,7 +2018,7 @@
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
     </row>
-    <row r="40" spans="1:8" ht="18.75">
+    <row r="40" spans="1:8" ht="18">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="12"/>
@@ -2259,10 +2047,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18876574-07EF-43D9-A34F-295A991584F3}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -2778,13 +2566,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5011F223-0C6D-4F39-9B4C-A9EA28CB4875}">
   <dimension ref="A2:H12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="2" max="2" width="51.85546875" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" customWidth="1"/>
+    <col min="2" max="2" width="51.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="18.75">
+    <row r="2" spans="1:8" ht="18">
       <c r="A2" s="10" t="s">
         <v>77</v>
       </c>
@@ -2864,7 +2652,7 @@
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:8" ht="18.75">
+    <row r="8" spans="1:8" ht="18">
       <c r="A8" s="10" t="s">
         <v>83</v>
       </c>
